--- a/ECB_stdev_lt.xlsx
+++ b/ECB_stdev_lt.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -130,13 +130,13 @@
         <v>5.0561127662658691</v>
       </c>
       <c r="C5" s="2">
-        <v>5.0083060264587402</v>
+        <v>5.0090365409851074</v>
       </c>
       <c r="D5" s="2">
         <v>5.1511406898498535</v>
       </c>
       <c r="E5" s="2">
-        <v>5.0762591361999512</v>
+        <v>5.0760998725891113</v>
       </c>
     </row>
     <row r="6">
@@ -147,13 +147,13 @@
         <v>5.2347140312194824</v>
       </c>
       <c r="C6" s="2">
-        <v>5.180595874786377</v>
+        <v>5.1798534393310547</v>
       </c>
       <c r="D6" s="2">
         <v>5.1738119125366211</v>
       </c>
       <c r="E6" s="2">
-        <v>5.0988507270812988</v>
+        <v>5.0985045433044434</v>
       </c>
     </row>
     <row r="7">
@@ -164,13 +164,13 @@
         <v>5.3309907913208008</v>
       </c>
       <c r="C7" s="2">
-        <v>5.2569370269775391</v>
+        <v>5.2580695152282715</v>
       </c>
       <c r="D7" s="2">
         <v>5.1854434013366699</v>
       </c>
       <c r="E7" s="2">
-        <v>5.1142368316650391</v>
+        <v>5.1138744354248047</v>
       </c>
     </row>
     <row r="8">
@@ -181,13 +181,13 @@
         <v>5.3025498390197754</v>
       </c>
       <c r="C8" s="2">
-        <v>5.2174882888793945</v>
+        <v>5.2179961204528809</v>
       </c>
       <c r="D8" s="2">
         <v>5.1646366119384766</v>
       </c>
       <c r="E8" s="2">
-        <v>5.0969171524047852</v>
+        <v>5.0968513488769531</v>
       </c>
     </row>
     <row r="9">
@@ -198,13 +198,13 @@
         <v>4.8313360214233398</v>
       </c>
       <c r="C9" s="2">
-        <v>4.7179679870605469</v>
+        <v>4.7155442237854004</v>
       </c>
       <c r="D9" s="2">
         <v>5.1804099082946777</v>
       </c>
       <c r="E9" s="2">
-        <v>5.1106996536254883</v>
+        <v>5.1106481552124023</v>
       </c>
     </row>
     <row r="10">
@@ -215,13 +215,13 @@
         <v>5.2871694564819336</v>
       </c>
       <c r="C10" s="2">
-        <v>5.2118101119995117</v>
+        <v>5.2105278968811035</v>
       </c>
       <c r="D10" s="2">
         <v>5.1714720726013184</v>
       </c>
       <c r="E10" s="2">
-        <v>5.1036257743835449</v>
+        <v>5.103299617767334</v>
       </c>
     </row>
     <row r="11">
@@ -232,13 +232,13 @@
         <v>5.2552323341369629</v>
       </c>
       <c r="C11" s="2">
-        <v>5.2065525054931641</v>
+        <v>5.2060928344726562</v>
       </c>
       <c r="D11" s="2">
         <v>5.1470808982849121</v>
       </c>
       <c r="E11" s="2">
-        <v>5.0792875289916992</v>
+        <v>5.0794863700866699</v>
       </c>
     </row>
     <row r="12">
@@ -249,13 +249,13 @@
         <v>5.0189886093139648</v>
       </c>
       <c r="C12" s="2">
-        <v>4.9756793975830078</v>
+        <v>4.977691650390625</v>
       </c>
       <c r="D12" s="2">
         <v>5.1537728309631348</v>
       </c>
       <c r="E12" s="2">
-        <v>5.0889816284179688</v>
+        <v>5.0894522666931152</v>
       </c>
     </row>
     <row r="13">
@@ -266,13 +266,13 @@
         <v>5.3065948486328125</v>
       </c>
       <c r="C13" s="2">
-        <v>5.2209606170654297</v>
+        <v>5.2210226058959961</v>
       </c>
       <c r="D13" s="2">
         <v>5.1076703071594238</v>
       </c>
       <c r="E13" s="2">
-        <v>5.0488548278808594</v>
+        <v>5.049415111541748</v>
       </c>
     </row>
     <row r="14">
@@ -283,13 +283,13 @@
         <v>4.975672721862793</v>
       </c>
       <c r="C14" s="2">
-        <v>4.944638729095459</v>
+        <v>4.9428973197937012</v>
       </c>
       <c r="D14" s="2">
         <v>5.0712623596191406</v>
       </c>
       <c r="E14" s="2">
-        <v>5.0137906074523926</v>
+        <v>5.0145683288574219</v>
       </c>
     </row>
     <row r="15">
@@ -300,13 +300,13 @@
         <v>5.0151915550231934</v>
       </c>
       <c r="C15" s="2">
-        <v>4.9615521430969238</v>
+        <v>4.9655346870422363</v>
       </c>
       <c r="D15" s="2">
         <v>5.1019768714904785</v>
       </c>
       <c r="E15" s="2">
-        <v>5.0443763732910156</v>
+        <v>5.0452413558959961</v>
       </c>
     </row>
     <row r="16">
@@ -317,13 +317,13 @@
         <v>5.3912186622619629</v>
       </c>
       <c r="C16" s="2">
-        <v>5.3441829681396484</v>
+        <v>5.3477621078491211</v>
       </c>
       <c r="D16" s="2">
         <v>5.0802431106567383</v>
       </c>
       <c r="E16" s="2">
-        <v>5.0197534561157227</v>
+        <v>5.0206170082092285</v>
       </c>
     </row>
     <row r="17">
@@ -334,13 +334,13 @@
         <v>4.8876276016235352</v>
       </c>
       <c r="C17" s="2">
-        <v>4.8563470840454102</v>
+        <v>4.8576607704162598</v>
       </c>
       <c r="D17" s="2">
         <v>5.0533018112182617</v>
       </c>
       <c r="E17" s="2">
-        <v>4.994544506072998</v>
+        <v>4.9950718879699707</v>
       </c>
     </row>
     <row r="18">
@@ -351,13 +351,13 @@
         <v>4.503664493560791</v>
       </c>
       <c r="C18" s="2">
-        <v>4.4023919105529785</v>
+        <v>4.401923656463623</v>
       </c>
       <c r="D18" s="2">
         <v>5.0443964004516602</v>
       </c>
       <c r="E18" s="2">
-        <v>4.9905996322631836</v>
+        <v>4.991117000579834</v>
       </c>
     </row>
     <row r="19">
@@ -368,13 +368,13 @@
         <v>5.5636019706726074</v>
       </c>
       <c r="C19" s="2">
-        <v>5.4870815277099609</v>
+        <v>5.4865880012512207</v>
       </c>
       <c r="D19" s="2">
         <v>5.0022244453430176</v>
       </c>
       <c r="E19" s="2">
-        <v>4.9392385482788086</v>
+        <v>4.9397368431091309</v>
       </c>
     </row>
     <row r="20">
@@ -385,13 +385,13 @@
         <v>5.059626579284668</v>
       </c>
       <c r="C20" s="2">
-        <v>4.9849457740783691</v>
+        <v>4.984473705291748</v>
       </c>
       <c r="D20" s="2">
         <v>5.0238499641418457</v>
       </c>
       <c r="E20" s="2">
-        <v>4.9605741500854492</v>
+        <v>4.9603285789489746</v>
       </c>
     </row>
     <row r="21">
@@ -402,13 +402,13 @@
         <v>4.776517391204834</v>
       </c>
       <c r="C21" s="2">
-        <v>4.7488002777099609</v>
+        <v>4.7477860450744629</v>
       </c>
       <c r="D21" s="2">
         <v>4.9920597076416016</v>
       </c>
       <c r="E21" s="2">
-        <v>4.9281167984008789</v>
+        <v>4.9277467727661133</v>
       </c>
     </row>
     <row r="22">
@@ -419,13 +419,13 @@
         <v>5.2264485359191895</v>
       </c>
       <c r="C22" s="2">
-        <v>5.185457706451416</v>
+        <v>5.185427188873291</v>
       </c>
       <c r="D22" s="2">
         <v>5.0657110214233398</v>
       </c>
       <c r="E22" s="2">
-        <v>5.0045766830444336</v>
+        <v>5.0042362213134766</v>
       </c>
     </row>
     <row r="23">
@@ -436,13 +436,13 @@
         <v>4.5961227416992188</v>
       </c>
       <c r="C23" s="2">
-        <v>4.4823884963989258</v>
+        <v>4.4804749488830566</v>
       </c>
       <c r="D23" s="2">
         <v>5.1422371864318848</v>
       </c>
       <c r="E23" s="2">
-        <v>5.0837841033935547</v>
+        <v>5.083345890045166</v>
       </c>
     </row>
     <row r="24">
@@ -453,13 +453,13 @@
         <v>5.2098236083984375</v>
       </c>
       <c r="C24" s="2">
-        <v>5.1535735130310059</v>
+        <v>5.1508607864379883</v>
       </c>
       <c r="D24" s="2">
         <v>5.1749086380004883</v>
       </c>
       <c r="E24" s="2">
-        <v>5.1259121894836426</v>
+        <v>5.1255917549133301</v>
       </c>
     </row>
     <row r="25">
@@ -470,13 +470,13 @@
         <v>5.1051058769226074</v>
       </c>
       <c r="C25" s="2">
-        <v>5.0520658493041992</v>
+        <v>5.0545248985290527</v>
       </c>
       <c r="D25" s="2">
         <v>5.3279900550842285</v>
       </c>
       <c r="E25" s="2">
-        <v>5.2856388092041016</v>
+        <v>5.2869772911071777</v>
       </c>
     </row>
     <row r="26">
@@ -487,13 +487,13 @@
         <v>5.5504865646362305</v>
       </c>
       <c r="C26" s="2">
-        <v>5.5444831848144531</v>
+        <v>5.5460672378540039</v>
       </c>
       <c r="D26" s="2">
         <v>5.5129051208496094</v>
       </c>
       <c r="E26" s="2">
-        <v>5.4715142250061035</v>
+        <v>5.4745917320251465</v>
       </c>
     </row>
     <row r="27">
@@ -504,13 +504,13 @@
         <v>5.1924009323120117</v>
       </c>
       <c r="C27" s="2">
-        <v>5.1152591705322266</v>
+        <v>5.1139087677001953</v>
       </c>
       <c r="D27" s="2">
         <v>5.630683422088623</v>
       </c>
       <c r="E27" s="2">
-        <v>5.5879006385803223</v>
+        <v>5.5914473533630371</v>
       </c>
     </row>
     <row r="28">
@@ -521,13 +521,13 @@
         <v>5.8576445579528809</v>
       </c>
       <c r="C28" s="2">
-        <v>5.8662357330322266</v>
+        <v>5.8668036460876465</v>
       </c>
       <c r="D28" s="2">
         <v>5.835695743560791</v>
       </c>
       <c r="E28" s="2">
-        <v>5.8015623092651367</v>
+        <v>5.8062129020690918</v>
       </c>
     </row>
     <row r="29">
@@ -538,13 +538,13 @@
         <v>6.4373588562011719</v>
       </c>
       <c r="C29" s="2">
-        <v>6.4224839210510254</v>
+        <v>6.4369416236877441</v>
       </c>
       <c r="D29" s="2">
         <v>6.0082602500915527</v>
       </c>
       <c r="E29" s="2">
-        <v>5.9782395362854004</v>
+        <v>5.9839887619018555</v>
       </c>
     </row>
     <row r="30">
@@ -555,13 +555,13 @@
         <v>6.4407534599304199</v>
       </c>
       <c r="C30" s="2">
-        <v>6.4216823577880859</v>
+        <v>6.4363155364990234</v>
       </c>
       <c r="D30" s="2">
         <v>6.2259507179260254</v>
       </c>
       <c r="E30" s="2">
-        <v>6.2029051780700684</v>
+        <v>6.2098512649536133</v>
       </c>
     </row>
     <row r="31">
@@ -572,13 +572,13 @@
         <v>6.2864542007446289</v>
       </c>
       <c r="C31" s="2">
-        <v>6.2329339981079102</v>
+        <v>6.2371273040771484</v>
       </c>
       <c r="D31" s="2">
         <v>6.4068880081176758</v>
       </c>
       <c r="E31" s="2">
-        <v>6.3807382583618164</v>
+        <v>6.3881034851074219</v>
       </c>
     </row>
     <row r="32">
@@ -589,13 +589,13 @@
         <v>6.4412341117858887</v>
       </c>
       <c r="C32" s="2">
-        <v>6.4053440093994141</v>
+        <v>6.4133658409118652</v>
       </c>
       <c r="D32" s="2">
         <v>6.5773634910583496</v>
       </c>
       <c r="E32" s="2">
-        <v>6.557830810546875</v>
+        <v>6.5668954849243164</v>
       </c>
     </row>
     <row r="33">
@@ -606,13 +606,13 @@
         <v>6.7629036903381348</v>
       </c>
       <c r="C33" s="2">
-        <v>6.7436680793762207</v>
+        <v>6.7508454322814941</v>
       </c>
       <c r="D33" s="2">
         <v>6.6679368019104004</v>
       </c>
       <c r="E33" s="2">
-        <v>6.6444807052612305</v>
+        <v>6.6540117263793945</v>
       </c>
     </row>
     <row r="34">
@@ -623,13 +623,13 @@
         <v>7.0643215179443359</v>
       </c>
       <c r="C34" s="2">
-        <v>7.0740551948547363</v>
+        <v>7.0872840881347656</v>
       </c>
       <c r="D34" s="2">
         <v>6.7084560394287109</v>
       </c>
       <c r="E34" s="2">
-        <v>6.689420223236084</v>
+        <v>6.6985764503479004</v>
       </c>
     </row>
     <row r="35">
@@ -640,13 +640,13 @@
         <v>7.178919792175293</v>
       </c>
       <c r="C35" s="2">
-        <v>7.1449832916259766</v>
+        <v>7.1503396034240723</v>
       </c>
       <c r="D35" s="2">
         <v>6.7258601188659668</v>
       </c>
       <c r="E35" s="2">
-        <v>6.7020959854125977</v>
+        <v>6.7097682952880859</v>
       </c>
     </row>
     <row r="36">
@@ -657,13 +657,13 @@
         <v>6.7266831398010254</v>
       </c>
       <c r="C36" s="2">
-        <v>6.7090897560119629</v>
+        <v>6.7230377197265625</v>
       </c>
       <c r="D36" s="2">
         <v>6.7896151542663574</v>
       </c>
       <c r="E36" s="2">
-        <v>6.7660746574401855</v>
+        <v>6.773552417755127</v>
       </c>
     </row>
     <row r="37">
@@ -674,13 +674,13 @@
         <v>6.6728005409240723</v>
       </c>
       <c r="C37" s="2">
-        <v>6.6460857391357422</v>
+        <v>6.6508498191833496</v>
       </c>
       <c r="D37" s="2">
         <v>6.8018803596496582</v>
       </c>
       <c r="E37" s="2">
-        <v>6.7728581428527832</v>
+        <v>6.7793154716491699</v>
       </c>
     </row>
     <row r="38">
@@ -691,13 +691,13 @@
         <v>6.802034854888916</v>
       </c>
       <c r="C38" s="2">
-        <v>6.8269381523132324</v>
+        <v>6.8380222320556641</v>
       </c>
       <c r="D38" s="2">
         <v>6.7918248176574707</v>
       </c>
       <c r="E38" s="2">
-        <v>6.7536067962646484</v>
+        <v>6.758324146270752</v>
       </c>
     </row>
     <row r="39">
@@ -708,13 +708,13 @@
         <v>6.5973906517028809</v>
       </c>
       <c r="C39" s="2">
-        <v>6.5357670783996582</v>
+        <v>6.5370426177978516</v>
       </c>
       <c r="D39" s="2">
         <v>6.7330832481384277</v>
       </c>
       <c r="E39" s="2">
-        <v>6.6841130256652832</v>
+        <v>6.6872687339782715</v>
       </c>
     </row>
     <row r="40">
@@ -725,13 +725,13 @@
         <v>6.8602485656738281</v>
       </c>
       <c r="C40" s="2">
-        <v>6.8087425231933594</v>
+        <v>6.811182975769043</v>
       </c>
       <c r="D40" s="2">
         <v>6.6376562118530273</v>
       </c>
       <c r="E40" s="2">
-        <v>6.587486743927002</v>
+        <v>6.5905470848083496</v>
       </c>
     </row>
     <row r="41">
@@ -742,13 +742,13 @@
         <v>6.5516200065612793</v>
       </c>
       <c r="C41" s="2">
-        <v>6.4663949012756348</v>
+        <v>6.465235710144043</v>
       </c>
       <c r="D41" s="2">
         <v>6.6009950637817383</v>
       </c>
       <c r="E41" s="2">
-        <v>6.5504288673400879</v>
+        <v>6.5523471832275391</v>
       </c>
     </row>
     <row r="42">
@@ -759,13 +759,13 @@
         <v>6.6724038124084473</v>
       </c>
       <c r="C42" s="2">
-        <v>6.5704026222229004</v>
+        <v>6.5619239807128906</v>
       </c>
       <c r="D42" s="2">
         <v>6.5184154510498047</v>
       </c>
       <c r="E42" s="2">
-        <v>6.463472843170166</v>
+        <v>6.4647855758666992</v>
       </c>
     </row>
     <row r="43">
@@ -776,13 +776,13 @@
         <v>6.535649299621582</v>
       </c>
       <c r="C43" s="2">
-        <v>6.4486150741577148</v>
+        <v>6.4477834701538086</v>
       </c>
       <c r="D43" s="2">
         <v>6.4262270927429199</v>
       </c>
       <c r="E43" s="2">
-        <v>6.3613138198852539</v>
+        <v>6.3606886863708496</v>
       </c>
     </row>
     <row r="44">
@@ -793,13 +793,13 @@
         <v>6.3200769424438477</v>
       </c>
       <c r="C44" s="2">
-        <v>6.2753458023071289</v>
+        <v>6.2798447608947754</v>
       </c>
       <c r="D44" s="2">
         <v>6.3099102973937988</v>
       </c>
       <c r="E44" s="2">
-        <v>6.2453608512878418</v>
+        <v>6.243927001953125</v>
       </c>
     </row>
     <row r="45">
@@ -810,13 +810,13 @@
         <v>6.3967313766479492</v>
       </c>
       <c r="C45" s="2">
-        <v>6.3755683898925781</v>
+        <v>6.379237174987793</v>
       </c>
       <c r="D45" s="2">
         <v>6.1550860404968262</v>
       </c>
       <c r="E45" s="2">
-        <v>6.0911006927490234</v>
+        <v>6.0894198417663574</v>
       </c>
     </row>
     <row r="46">
@@ -827,13 +827,13 @@
         <v>5.9295821189880371</v>
       </c>
       <c r="C46" s="2">
-        <v>5.8634829521179199</v>
+        <v>5.8627972602844238</v>
       </c>
       <c r="D46" s="2">
         <v>6.0590648651123047</v>
       </c>
       <c r="E46" s="2">
-        <v>6.001129150390625</v>
+        <v>5.9998083114624023</v>
       </c>
     </row>
     <row r="47">
@@ -844,13 +844,13 @@
         <v>5.9723429679870605</v>
       </c>
       <c r="C47" s="2">
-        <v>5.9075040817260742</v>
+        <v>5.9011492729187012</v>
       </c>
       <c r="D47" s="2">
         <v>5.9663729667663574</v>
       </c>
       <c r="E47" s="2">
-        <v>5.9087715148925781</v>
+        <v>5.9079642295837402</v>
       </c>
     </row>
     <row r="48">
@@ -861,13 +861,13 @@
         <v>5.5505385398864746</v>
       </c>
       <c r="C48" s="2">
-        <v>5.492192268371582</v>
+        <v>5.4861903190612793</v>
       </c>
       <c r="D48" s="2">
         <v>5.9031972885131836</v>
       </c>
       <c r="E48" s="2">
-        <v>5.8488078117370605</v>
+        <v>5.8482208251953125</v>
       </c>
     </row>
     <row r="49">
@@ -878,13 +878,13 @@
         <v>5.466829776763916</v>
       </c>
       <c r="C49" s="2">
-        <v>5.4204001426696777</v>
+        <v>5.4206180572509766</v>
       </c>
       <c r="D49" s="2">
         <v>5.8723864555358887</v>
       </c>
       <c r="E49" s="2">
-        <v>5.8128242492675781</v>
+        <v>5.8114585876464844</v>
       </c>
     </row>
     <row r="50">
@@ -895,13 +895,13 @@
         <v>5.6874308586120605</v>
       </c>
       <c r="C50" s="2">
-        <v>5.6566510200500488</v>
+        <v>5.6587324142456055</v>
       </c>
       <c r="D50" s="2">
         <v>5.7986288070678711</v>
       </c>
       <c r="E50" s="2">
-        <v>5.7273802757263184</v>
+        <v>5.7244873046875</v>
       </c>
     </row>
     <row r="51">
@@ -912,13 +912,13 @@
         <v>5.8381743431091309</v>
       </c>
       <c r="C51" s="2">
-        <v>5.7391834259033203</v>
+        <v>5.7353272438049316</v>
       </c>
       <c r="D51" s="2">
         <v>5.804379940032959</v>
       </c>
       <c r="E51" s="2">
-        <v>5.7291460037231445</v>
+        <v>5.7260560989379883</v>
       </c>
     </row>
     <row r="52">
@@ -929,13 +929,13 @@
         <v>5.9670672416687012</v>
       </c>
       <c r="C52" s="2">
-        <v>5.9089431762695312</v>
+        <v>5.910092830657959</v>
       </c>
       <c r="D52" s="2">
         <v>5.755403995513916</v>
       </c>
       <c r="E52" s="2">
-        <v>5.6727848052978516</v>
+        <v>5.6695308685302734</v>
       </c>
     </row>
     <row r="53">
@@ -946,13 +946,13 @@
         <v>6.0427818298339844</v>
       </c>
       <c r="C53" s="2">
-        <v>5.9514932632446289</v>
+        <v>5.9489808082580566</v>
       </c>
       <c r="D53" s="2">
         <v>5.7368502616882324</v>
       </c>
       <c r="E53" s="2">
-        <v>5.6481046676635742</v>
+        <v>5.6443333625793457</v>
       </c>
     </row>
     <row r="54">
@@ -963,13 +963,13 @@
         <v>5.7329096794128418</v>
       </c>
       <c r="C54" s="2">
-        <v>5.6065735816955566</v>
+        <v>5.5964970588684082</v>
       </c>
       <c r="D54" s="2">
         <v>5.7360215187072754</v>
       </c>
       <c r="E54" s="2">
-        <v>5.6395883560180664</v>
+        <v>5.6349725723266602</v>
       </c>
     </row>
     <row r="55">
@@ -980,13 +980,13 @@
         <v>5.9813456535339355</v>
       </c>
       <c r="C55" s="2">
-        <v>5.8793721199035645</v>
+        <v>5.8769164085388184</v>
       </c>
       <c r="D55" s="2">
         <v>5.7184667587280273</v>
       </c>
       <c r="E55" s="2">
-        <v>5.614771842956543</v>
+        <v>5.6091651916503906</v>
       </c>
     </row>
     <row r="56">
@@ -997,13 +997,13 @@
         <v>5.5315570831298828</v>
       </c>
       <c r="C56" s="2">
-        <v>5.4002552032470703</v>
+        <v>5.3924212455749512</v>
       </c>
       <c r="D56" s="2">
         <v>5.6665811538696289</v>
       </c>
       <c r="E56" s="2">
-        <v>5.5613002777099609</v>
+        <v>5.555330753326416</v>
       </c>
     </row>
     <row r="57">
@@ -1014,13 +1014,13 @@
         <v>5.3835568428039551</v>
       </c>
       <c r="C57" s="2">
-        <v>5.2700705528259277</v>
+        <v>5.2594151496887207</v>
       </c>
       <c r="D57" s="2">
         <v>5.5828619003295898</v>
       </c>
       <c r="E57" s="2">
-        <v>5.4797205924987793</v>
+        <v>5.4738421440124512</v>
       </c>
     </row>
     <row r="58">
@@ -1031,13 +1031,13 @@
         <v>5.4593696594238281</v>
       </c>
       <c r="C58" s="2">
-        <v>5.3437538146972656</v>
+        <v>5.3363685607910156</v>
       </c>
       <c r="D58" s="2">
         <v>5.5301661491394043</v>
       </c>
       <c r="E58" s="2">
-        <v>5.4284706115722656</v>
+        <v>5.422797679901123</v>
       </c>
     </row>
     <row r="59">
@@ -1048,13 +1048,13 @@
         <v>5.5294394493103027</v>
       </c>
       <c r="C59" s="2">
-        <v>5.4333004951477051</v>
+        <v>5.4264659881591797</v>
       </c>
       <c r="D59" s="2">
         <v>5.5471291542053223</v>
       </c>
       <c r="E59" s="2">
-        <v>5.4447407722473145</v>
+        <v>5.4396648406982422</v>
       </c>
     </row>
     <row r="60">
@@ -1065,13 +1065,13 @@
         <v>5.3712029457092285</v>
       </c>
       <c r="C60" s="2">
-        <v>5.2579398155212402</v>
+        <v>5.2508196830749512</v>
       </c>
       <c r="D60" s="2">
         <v>5.5099964141845703</v>
       </c>
       <c r="E60" s="2">
-        <v>5.4059686660766602</v>
+        <v>5.4005346298217773</v>
       </c>
     </row>
     <row r="61">
@@ -1082,13 +1082,13 @@
         <v>5.2135939598083496</v>
       </c>
       <c r="C61" s="2">
-        <v>5.1747245788574219</v>
+        <v>5.1766934394836426</v>
       </c>
       <c r="D61" s="2">
-        <v>5.5073013305664062</v>
+        <v>5.5200200080871582</v>
       </c>
       <c r="E61" s="2">
-        <v>5.4066824913024902</v>
+        <v>5.4142451286315918</v>
       </c>
     </row>
     <row r="62">
@@ -1099,13 +1099,13 @@
         <v>5.5685210227966309</v>
       </c>
       <c r="C62" s="2">
-        <v>5.4902467727661133</v>
+        <v>5.4895796775817871</v>
       </c>
       <c r="D62" s="2">
-        <v>5.5249791145324707</v>
+        <v>5.5416727066040039</v>
       </c>
       <c r="E62" s="2">
-        <v>5.4261984825134277</v>
+        <v>5.4396729469299316</v>
       </c>
     </row>
     <row r="63">
@@ -1116,13 +1116,13 @@
         <v>5.8855748176574707</v>
       </c>
       <c r="C63" s="2">
-        <v>5.7530045509338379</v>
+        <v>5.7483048439025879</v>
       </c>
       <c r="D63" s="2">
-        <v>5.5359139442443848</v>
+        <v>5.5564827919006348</v>
       </c>
       <c r="E63" s="2">
-        <v>5.4399394989013672</v>
+        <v>5.4500861167907715</v>
       </c>
     </row>
     <row r="64">
@@ -1133,23 +1133,176 @@
         <v>5.6471514701843262</v>
       </c>
       <c r="C64" s="2">
-        <v>5.5304203033447266</v>
+        <v>5.524744987487793</v>
       </c>
       <c r="D64" s="2">
-        <v>5.5372090339660645</v>
+        <v>5.5600228309631348</v>
       </c>
       <c r="E64" s="2">
-        <v>5.4412670135498047</v>
+        <v>5.451718807220459</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="B65" s="2">
+        <v>5.6217679977416992</v>
+      </c>
+      <c r="C65" s="2">
+        <v>5.5158143043518066</v>
+      </c>
+      <c r="D65" s="2">
+        <v>5.6199660301208496</v>
+      </c>
+      <c r="E65" s="2">
+        <v>5.5114808082580566</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B66" s="2">
+        <v>5.578432559967041</v>
+      </c>
+      <c r="C66" s="2">
+        <v>5.4882664680480957</v>
+      </c>
+      <c r="D66" s="2">
+        <v>5.6572079658508301</v>
+      </c>
+      <c r="E66" s="2">
+        <v>5.539055347442627</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B67" s="2">
+        <v>5.5926609039306641</v>
+      </c>
+      <c r="C67" s="2">
+        <v>5.430084228515625</v>
+      </c>
+      <c r="D67" s="2">
+        <v>5.6509947776794434</v>
+      </c>
+      <c r="E67" s="2">
+        <v>5.5251846313476562</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B68" s="2">
+        <v>5.5612998008728027</v>
+      </c>
+      <c r="C68" s="2">
+        <v>5.4411630630493164</v>
+      </c>
+      <c r="D68" s="2">
+        <v>5.6205148696899414</v>
+      </c>
+      <c r="E68" s="2">
+        <v>5.4965176582336426</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B69" s="2">
+        <v>5.9106912612915039</v>
+      </c>
+      <c r="C69" s="2">
+        <v>5.7886781692504883</v>
+      </c>
+      <c r="D69" s="2">
+        <v>5.5798149108886719</v>
+      </c>
+      <c r="E69" s="2">
+        <v>5.4556231498718262</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B70" s="2">
+        <v>5.5487737655639648</v>
+      </c>
+      <c r="C70" s="2">
+        <v>5.4248642921447754</v>
+      </c>
+      <c r="D70" s="2">
+        <v>5.5745706558227539</v>
+      </c>
+      <c r="E70" s="2">
+        <v>5.4480996131896973</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B71" s="2">
+        <v>5.5125994682312012</v>
+      </c>
+      <c r="C71" s="2">
+        <v>5.3647408485412598</v>
+      </c>
+      <c r="D71" s="2">
+        <v>5.5740189552307129</v>
+      </c>
+      <c r="E71" s="2">
+        <v>5.4423613548278809</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B72" s="2">
+        <v>5.6112585067749023</v>
+      </c>
+      <c r="C72" s="2">
+        <v>5.4903039932250977</v>
+      </c>
+      <c r="D72" s="2">
+        <v>5.5709123611450195</v>
+      </c>
+      <c r="E72" s="2">
+        <v>5.4444074630737305</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B73" s="2">
+        <v>5.2808499336242676</v>
+      </c>
+      <c r="C73" s="2">
+        <v>5.1566948890686035</v>
+      </c>
+      <c r="D73" s="2">
+        <v>5.5728344917297363</v>
+      </c>
+      <c r="E73" s="2">
+        <v>5.4450564384460449</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
     </row>
   </sheetData>
 </worksheet>
